--- a/03_Outputs/all/idx5_viviendas_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx5_viviendas_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2911383316195094</v>
+        <v>0.2911383316195085</v>
       </c>
       <c r="D2">
-        <v>0.1231025615265198</v>
+        <v>0.1231025615265194</v>
       </c>
       <c r="E2">
         <v>12.3</v>
@@ -420,7 +420,7 @@
         <v>0.5527327280676585</v>
       </c>
       <c r="D3">
-        <v>0.2337130060688665</v>
+        <v>0.2337130060688664</v>
       </c>
       <c r="E3">
         <v>23.4</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3073493289592407</v>
+        <v>0.3073493289592402</v>
       </c>
       <c r="D4">
-        <v>0.1299570876424028</v>
+        <v>0.1299570876424025</v>
       </c>
       <c r="E4">
         <v>13</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.5279486835876077</v>
+        <v>0.5279486835876082</v>
       </c>
       <c r="D5">
-        <v>0.2232335225068435</v>
+        <v>0.2232335225068436</v>
       </c>
       <c r="E5">
         <v>22.3</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3169836877886586</v>
+        <v>0.316983687788659</v>
       </c>
       <c r="D6">
-        <v>0.134030801481352</v>
+        <v>0.1340308014813521</v>
       </c>
       <c r="E6">
         <v>13.4</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3688535242437163</v>
+        <v>0.3688535242437173</v>
       </c>
       <c r="D7">
-        <v>0.1559630207740155</v>
+        <v>0.1559630207740159</v>
       </c>
       <c r="E7">
         <v>15.6</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.6171870822010579</v>
+        <v>0.6171870822010581</v>
       </c>
       <c r="D8">
         <v>0.3008193635084002</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.2047026803622318</v>
+        <v>-0.204702680362231</v>
       </c>
       <c r="D9">
-        <v>0.09977287566587456</v>
+        <v>0.09977287566587417</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.6473457543048433</v>
+        <v>0.6473457543048439</v>
       </c>
       <c r="D10">
-        <v>0.3155188165723965</v>
+        <v>0.3155188165723967</v>
       </c>
       <c r="E10">
         <v>31.6</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.3638974134665841</v>
+        <v>-0.3638974134665832</v>
       </c>
       <c r="D11">
-        <v>0.1773650023765571</v>
+        <v>0.1773650023765566</v>
       </c>
       <c r="E11">
         <v>17.7</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.1394115209845929</v>
+        <v>-0.1394115209845935</v>
       </c>
       <c r="D12">
-        <v>0.0679497128468113</v>
+        <v>0.0679497128468116</v>
       </c>
       <c r="E12">
         <v>6.8</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.07914223202088427</v>
+        <v>-0.07914223202088516</v>
       </c>
       <c r="D13">
-        <v>0.03857422902996029</v>
+        <v>0.03857422902996072</v>
       </c>
       <c r="E13">
         <v>3.9</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.3199783290212269</v>
+        <v>-0.3199783290212264</v>
       </c>
       <c r="D14">
-        <v>0.1390087286276186</v>
+        <v>0.1390087286276182</v>
       </c>
       <c r="E14">
         <v>13.9</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.3334871310540671</v>
+        <v>-0.3334871310540684</v>
       </c>
       <c r="D15">
-        <v>0.1448773804254181</v>
+        <v>0.1448773804254185</v>
       </c>
       <c r="E15">
         <v>14.5</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.2191070565433384</v>
+        <v>0.2191070565433392</v>
       </c>
       <c r="D16">
-        <v>0.09518705049993771</v>
+        <v>0.09518705049993796</v>
       </c>
       <c r="E16">
         <v>9.5</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.3157392572812474</v>
+        <v>-0.3157392572812479</v>
       </c>
       <c r="D17">
-        <v>0.1371671414959578</v>
+        <v>0.1371671414959579</v>
       </c>
       <c r="E17">
         <v>13.7</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.653490713501334</v>
+        <v>0.653490713501332</v>
       </c>
       <c r="D18">
-        <v>0.283897079941778</v>
+        <v>0.2838970799417768</v>
       </c>
       <c r="E18">
         <v>28.4</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.4600553324655945</v>
+        <v>0.4600553324655966</v>
       </c>
       <c r="D19">
-        <v>0.1998626190092899</v>
+        <v>0.1998626190092906</v>
       </c>
       <c r="E19">
         <v>20</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.1024234271586742</v>
+        <v>0.1024234271586735</v>
       </c>
       <c r="D20">
-        <v>0.06375959984559273</v>
+        <v>0.0637595998455923</v>
       </c>
       <c r="E20">
         <v>6.4</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.04214728289487909</v>
+        <v>0.04214728289487851</v>
       </c>
       <c r="D21">
-        <v>0.02623710186726455</v>
+        <v>0.0262371018672642</v>
       </c>
       <c r="E21">
         <v>2.6</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.009675745111864021</v>
+        <v>-0.009675745111863763</v>
       </c>
       <c r="D22">
-        <v>0.006023247353212129</v>
+        <v>0.006023247353211972</v>
       </c>
       <c r="E22">
         <v>0.6</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.05430628088229653</v>
+        <v>0.05430628088229612</v>
       </c>
       <c r="D23">
-        <v>0.03380619877904902</v>
+        <v>0.03380619877904879</v>
       </c>
       <c r="E23">
         <v>3.4</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.6368687094052957</v>
+        <v>0.6368687094052979</v>
       </c>
       <c r="D24">
-        <v>0.3964570918228816</v>
+        <v>0.3964570918228833</v>
       </c>
       <c r="E24">
         <v>39.6</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.7609786481284131</v>
+        <v>-0.7609786481284118</v>
       </c>
       <c r="D25">
-        <v>0.4737167603319999</v>
+        <v>0.4737167603319994</v>
       </c>
       <c r="E25">
         <v>47.4</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.6274511470660009</v>
+        <v>0.6274511470660014</v>
       </c>
       <c r="D26">
-        <v>0.2900675869751334</v>
+        <v>0.2900675869751336</v>
       </c>
       <c r="E26">
         <v>29</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.582479233722801</v>
+        <v>-0.5824792337228006</v>
       </c>
       <c r="D28">
         <v>0.2692772920715133</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.1252001590401588</v>
+        <v>0.1252001590401587</v>
       </c>
       <c r="D29">
-        <v>0.05787941928467254</v>
+        <v>0.0578794192846725</v>
       </c>
       <c r="E29">
         <v>5.8</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.1921055873696697</v>
+        <v>0.1921055873696691</v>
       </c>
       <c r="D30">
-        <v>0.08880947055930592</v>
+        <v>0.08880947055930567</v>
       </c>
       <c r="E30">
         <v>8.9</v>
@@ -1008,7 +1008,7 @@
         <v>0.2396194980627367</v>
       </c>
       <c r="D31">
-        <v>0.1107749183665759</v>
+        <v>0.110774918366576</v>
       </c>
       <c r="E31">
         <v>11.1</v>
@@ -1029,7 +1029,7 @@
         <v>-0.1665741456450177</v>
       </c>
       <c r="D32">
-        <v>0.08387158633248973</v>
+        <v>0.08387158633248963</v>
       </c>
       <c r="E32">
         <v>8.4</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.6185203505045034</v>
+        <v>-0.6185203505045032</v>
       </c>
       <c r="D33">
-        <v>0.3114305811076624</v>
+        <v>0.311430581107662</v>
       </c>
       <c r="E33">
         <v>31.1</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.3147956231953365</v>
+        <v>0.3147956231953368</v>
       </c>
       <c r="D34">
-        <v>0.158502438572809</v>
+        <v>0.1585024385728091</v>
       </c>
       <c r="E34">
         <v>15.9</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.6859543202101578</v>
+        <v>0.6859543202101586</v>
       </c>
       <c r="D35">
-        <v>0.3453841937166877</v>
+        <v>0.3453841937166878</v>
       </c>
       <c r="E35">
         <v>34.5</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.102612607129773</v>
+        <v>-0.1026126071297735</v>
       </c>
       <c r="D36">
-        <v>0.0516663741804641</v>
+        <v>0.05166637418046429</v>
       </c>
       <c r="E36">
         <v>5.2</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.09760465703299506</v>
+        <v>-0.09760465703299556</v>
       </c>
       <c r="D37">
-        <v>0.04914482608988695</v>
+        <v>0.04914482608988716</v>
       </c>
       <c r="E37">
         <v>4.9</v>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3715458715940225</v>
+        <v>0.3715458715940223</v>
       </c>
     </row>
     <row r="3">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2219417687494836</v>
+        <v>0.2219417687494839</v>
       </c>
     </row>
     <row r="4">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1606883916146165</v>
+        <v>0.1606883916146164</v>
       </c>
     </row>
     <row r="5">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1308007980197976</v>
+        <v>0.1308007980197975</v>
       </c>
     </row>
     <row r="6">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.08092914348127572</v>
+        <v>0.08092914348127575</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.03409402654080394</v>
+        <v>0.03409402654080403</v>
       </c>
     </row>
   </sheetData>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5279486835876077</v>
+        <v>0.5279486835876082</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.3688535242437163</v>
+        <v>0.3688535242437173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3169836877886586</v>
+        <v>0.316983687788659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3073493289592407</v>
+        <v>0.3073493289592402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.2911383316195094</v>
+        <v>0.2911383316195085</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6473457543048433</v>
+        <v>0.6473457543048439</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6171870822010579</v>
+        <v>0.6171870822010581</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3638974134665841</v>
+        <v>-0.3638974134665832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.2047026803622318</v>
+        <v>-0.204702680362231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1394115209845929</v>
+        <v>-0.1394115209845935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.07914223202088427</v>
+        <v>-0.07914223202088516</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
